--- a/ICME_density_pileup_search_PSP_SOLO/结果_PSP_多参数密度堆积区/PSP_ICME_密度堆积区结果.xlsx
+++ b/ICME_density_pileup_search_PSP_SOLO/结果_PSP_多参数密度堆积区/PSP_ICME_密度堆积区结果.xlsx
@@ -873,7 +873,7 @@
         <v>43539.74236111111</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>43539.375</v>
+        <v>43539.38888888889</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>43539.55416666667</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>43539.37569444445</v>
+        <v>43539.40208333333</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>43539.51666666667</v>
+        <v>43539.53472222222</v>
       </c>
       <c r="R3" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -911,18 +911,18 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="b">
         <v>0</v>
@@ -931,61 +931,61 @@
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.5400220648927</v>
+        <v>46.35084119487454</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.57834015025033</v>
+        <v>26.12282168732749</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.76384400782613</v>
+        <v>25.13376020060646</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.203136188134526</v>
+        <v>1.774342823668238</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.000519025846003</v>
+        <v>1.844166603998877</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5703232320220442</v>
+        <v>0.5808082990230607</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3977788836050738</v>
+        <v>0.2902087588519734</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0371800930128903</v>
+        <v>0.02917487023673123</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.43376950242607</v>
+        <v>2.001346552463337</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.33947835537457</v>
+        <v>19.9078280146666</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.2223342560195</v>
+        <v>13.79108325879611</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.41724532643954</v>
+        <v>9.377301838000616</v>
       </c>
       <c r="AM3" t="n">
-        <v>23.54289348522822</v>
+        <v>26.4126337369283</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.625381240647461</v>
+        <v>1.470687783868604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6041030710580744</v>
+        <v>0.5221396471157052</v>
       </c>
       <c r="AP3" t="n">
-        <v>98.02955665024631</v>
+        <v>96.8586387434555</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>43539.39791666667</v>
+        <v>43539.40208333333</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>43539.51388888889</v>
+        <v>43539.50694444445</v>
       </c>
       <c r="AS3" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44005.70277777778</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44005.1375</v>
+        <v>44005.15347222222</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>44005.37777777778</v>
@@ -1416,28 +1416,28 @@
         <v>30.96164191771555</v>
       </c>
       <c r="AC6" t="n">
-        <v>37.80875328341786</v>
+        <v>37.80875328341787</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.162899246757653</v>
+        <v>1.162899246757652</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9522998495769694</v>
+        <v>0.9522998495769691</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5593658678058875</v>
+        <v>0.5593658678058874</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2674795355904256</v>
+        <v>0.2674795355904255</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2786451285827458</v>
+        <v>0.2786451285827441</v>
       </c>
       <c r="AI6" t="n">
         <v>2.09124734186173</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.007448939268929</v>
+        <v>2.007448939268941</v>
       </c>
       <c r="AK6" t="n">
         <v>9.892509543069519</v>
@@ -1513,7 +1513,7 @@
         <v>44008.34375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44007.48541666667</v>
+        <v>44007.50347222222</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>44007.80138888889</v>
@@ -1571,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>76.63484738475142</v>
+        <v>76.63484738475138</v>
       </c>
       <c r="AB7" t="n">
         <v>107.5139742765961</v>
@@ -1580,10 +1580,10 @@
         <v>60.02611411358681</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7127896433964628</v>
+        <v>0.7127896433964626</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.27669179516995</v>
+        <v>1.276691795169949</v>
       </c>
       <c r="AF7" t="n">
         <v>0.7474191592141007</v>
@@ -1674,7 +1674,7 @@
         <v>44086.81597222222</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44086.43263888889</v>
+        <v>44086.44583333333</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>44086.61458333334</v>
@@ -1735,31 +1735,31 @@
         <v>65.86011344952865</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.4622410983131</v>
+        <v>104.462241098313</v>
       </c>
       <c r="AC8" t="n">
         <v>24.69597589062699</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6304681266367376</v>
+        <v>0.630468126636738</v>
       </c>
       <c r="AE8" t="n">
         <v>2.666835833546668</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.256341583997189</v>
+        <v>2.256341583997191</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12727997709059</v>
+        <v>1.127279977090591</v>
       </c>
       <c r="AH8" t="n">
         <v>0.3978976063207976</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.001580467898142</v>
+        <v>2.001580467898141</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5.670658853318296</v>
+        <v>5.670658853318301</v>
       </c>
       <c r="AK8" t="n">
         <v>7.076479454668577</v>
@@ -1835,7 +1835,7 @@
         <v>44347.03055555555</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44346.33888888889</v>
+        <v>44346.36458333334</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>44346.68263888889</v>
@@ -1858,13 +1858,13 @@
         <v>1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>44346.35763888889</v>
+        <v>44346.36458333334</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>44346.68263888889</v>
       </c>
       <c r="R9" t="n">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1893,61 +1893,61 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.77715385134136</v>
+        <v>13.91961662818051</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.397410298663157</v>
+        <v>6.302172510436288</v>
       </c>
       <c r="AC9" t="n">
         <v>41.92311052464775</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.153551704229494</v>
+        <v>2.208701301833593</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3286290945239235</v>
+        <v>0.3320272864771516</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1671640372518709</v>
+        <v>0.1699313122500153</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.04462900984794389</v>
+        <v>0.04108404325773587</v>
       </c>
       <c r="AH9" t="n">
         <v>0.0309001523669392</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.745636253670377</v>
+        <v>4.136187647938431</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.409812717646131</v>
+        <v>5.499368101233985</v>
       </c>
       <c r="AK9" t="n">
-        <v>17.31833834815611</v>
+        <v>17.34485022453632</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.678865863879522</v>
+        <v>7.63364560008049</v>
       </c>
       <c r="AM9" t="n">
         <v>28.20470524628957</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.593005863737543</v>
+        <v>2.272158170973176</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.6140230219365401</v>
+        <v>0.6149630025585215</v>
       </c>
       <c r="AP9" t="n">
         <v>90</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>44346.35763888889</v>
+        <v>44346.36458333334</v>
       </c>
       <c r="AR9" s="2" t="n">
         <v>44346.68263888889</v>
       </c>
       <c r="AS9" t="n">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>44358.37013888889</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44357.19236111111</v>
+        <v>44357.24375</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>44357.83611111111</v>
@@ -2060,13 +2060,13 @@
         <v>18.29547182947486</v>
       </c>
       <c r="AC10" t="n">
-        <v>24.87833150795528</v>
+        <v>24.87833150795529</v>
       </c>
       <c r="AD10" t="n">
         <v>1.167711926279329</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.8587328553506021</v>
+        <v>0.8587328553506015</v>
       </c>
       <c r="AF10" t="n">
         <v>0.4574782818759829</v>
@@ -2075,13 +2075,13 @@
         <v>0.40793689370368</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3787303476429545</v>
+        <v>0.3787303476429556</v>
       </c>
       <c r="AI10" t="n">
         <v>1.121443754994833</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.207926126657448</v>
+        <v>1.207926126657445</v>
       </c>
       <c r="AK10" t="n">
         <v>2.837633961479406</v>
@@ -2157,7 +2157,7 @@
         <v>44360.05</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44359.25069444445</v>
+        <v>44359.26458333333</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>44359.52083333334</v>
@@ -2221,25 +2221,25 @@
         <v>22.1606175205861</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.020585157214737</v>
+        <v>6.020585157214729</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.8320891583097584</v>
+        <v>0.8320891583097585</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.062760362791641</v>
+        <v>3.062760362791645</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1314486325958874</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.4165264091442418</v>
+        <v>0.416526409144242</v>
       </c>
       <c r="AH11" t="n">
         <v>0.01897434627903798</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.3155829491482908</v>
+        <v>0.3155829491482905</v>
       </c>
       <c r="AJ11" t="n">
         <v>6.927702839549525</v>
@@ -2318,7 +2318,7 @@
         <v>44372.25347222222</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44371.06111111111</v>
+        <v>44371.08958333333</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>44371.52291666667</v>
@@ -2376,19 +2376,19 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.70145542927281</v>
+        <v>24.70145542927276</v>
       </c>
       <c r="AB12" t="n">
         <v>35.64541814474165</v>
       </c>
       <c r="AC12" t="n">
-        <v>27.29989287356535</v>
+        <v>27.29989287356537</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.6929770140153826</v>
+        <v>0.692977014015381</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.9048187677392454</v>
+        <v>0.9048187677392427</v>
       </c>
       <c r="AF12" t="n">
         <v>0.06501663806813729</v>
@@ -2397,13 +2397,13 @@
         <v>0.3676192158640679</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1255192190576009</v>
+        <v>0.1255192190576011</v>
       </c>
       <c r="AI12" t="n">
         <v>0.1768586495548645</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.5179815374592246</v>
+        <v>0.5179815374592235</v>
       </c>
       <c r="AK12" t="n">
         <v>1.96185408182668</v>
@@ -2479,7 +2479,7 @@
         <v>44378.71666666667</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44377.62361111111</v>
+        <v>44377.65416666667</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>44378.08263888889</v>
@@ -2540,13 +2540,13 @@
         <v>23.37595397100399</v>
       </c>
       <c r="AB13" t="n">
-        <v>50.95810646752687</v>
+        <v>50.95810646752688</v>
       </c>
       <c r="AC13" t="n">
         <v>15.37466976524869</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.4587288577117823</v>
+        <v>0.4587288577117822</v>
       </c>
       <c r="AE13" t="n">
         <v>1.520419906763824</v>
@@ -2555,13 +2555,13 @@
         <v>0.04127320751975046</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5085900575653607</v>
+        <v>0.5085900575653602</v>
       </c>
       <c r="AH13" t="n">
         <v>0.01563794299439457</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.08115221071628262</v>
+        <v>0.08115221071628269</v>
       </c>
       <c r="AJ13" t="n">
         <v>2.639299013594362</v>
@@ -2640,7 +2640,7 @@
         <v>44388.77152777778</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44388.37916666667</v>
+        <v>44388.38472222222</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>44388.50138888889</v>
@@ -2960,7 +2960,7 @@
         <v>44466.525</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44465.37152777778</v>
+        <v>44465.43055555555</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>44466.07361111111</v>
@@ -3021,13 +3021,13 @@
         <v>18.49517322116432</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.58512227204116</v>
+        <v>18.58512227204115</v>
       </c>
       <c r="AC16" t="n">
         <v>15.28710655260971</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9951601582405429</v>
+        <v>0.9951601582405434</v>
       </c>
       <c r="AE16" t="n">
         <v>1.20985440622882</v>
@@ -3121,7 +3121,7 @@
         <v>44510.19305555556</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44509.68194444444</v>
+        <v>44509.69166666667</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>44509.86041666667</v>
@@ -3144,13 +3144,13 @@
         <v>1</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>44509.68402777778</v>
+        <v>44509.69166666667</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>44509.80694444444</v>
+        <v>44509.81180555555</v>
       </c>
       <c r="R17" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -3179,61 +3179,61 @@
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>66.21184636599149</v>
+        <v>64.71191882903405</v>
       </c>
       <c r="AB17" t="n">
-        <v>44.46220630804698</v>
+        <v>47.17626660664876</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.34553162786694</v>
+        <v>18.98760293854605</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.489171407897681</v>
+        <v>1.371704958524927</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.422591202953263</v>
+        <v>3.408114180524846</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.5344785059843485</v>
+        <v>0.5383562379233078</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.2669634992617208</v>
+        <v>0.2690845087058878</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01819288587091883</v>
+        <v>0.01690545351564978</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.00206585343102</v>
+        <v>2.000695768449966</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29.37843450327514</v>
+        <v>31.84512248813311</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.69960904731757</v>
+        <v>17.85568239376207</v>
       </c>
       <c r="AL17" t="n">
-        <v>11.76591345866521</v>
+        <v>12.66253986756007</v>
       </c>
       <c r="AM17" t="n">
-        <v>19.37324867149194</v>
+        <v>21.29541449944178</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.58930363656091</v>
+        <v>1.410118552874706</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.9652283602199543</v>
+        <v>0.8384754564993382</v>
       </c>
       <c r="AP17" t="n">
         <v>100</v>
       </c>
       <c r="AQ17" s="2" t="n">
-        <v>44509.68402777778</v>
+        <v>44509.69166666667</v>
       </c>
       <c r="AR17" s="2" t="n">
-        <v>44509.80694444444</v>
+        <v>44509.81180555555</v>
       </c>
       <c r="AS17" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44591.08333333334</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44589.99722222222</v>
+        <v>44590.04375</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>44590.58263888889</v>
@@ -3343,13 +3343,13 @@
         <v>28.74868522385019</v>
       </c>
       <c r="AB18" t="n">
-        <v>33.50490711530049</v>
+        <v>33.5049071153005</v>
       </c>
       <c r="AC18" t="n">
         <v>14.07322497367856</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.8580440209822786</v>
+        <v>0.8580440209822784</v>
       </c>
       <c r="AE18" t="n">
         <v>2.042792982960156</v>
@@ -3358,16 +3358,16 @@
         <v>0.2242777467933144</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1120493195959427</v>
+        <v>0.1120493195959425</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03059083096928011</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.001598471120349</v>
+        <v>2.001598471120353</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7.331534962830474</v>
+        <v>7.331534962830475</v>
       </c>
       <c r="AK18" t="n">
         <v>10.25467656438411</v>
@@ -3602,7 +3602,7 @@
         <v>44684.20486111111</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44683.72083333333</v>
+        <v>44683.74166666667</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>44683.97916666666</v>
@@ -3663,16 +3663,16 @@
         <v>8.12744483834221</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.751682697236542</v>
+        <v>7.751682697236538</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.204746558268857</v>
+        <v>8.204746558268861</v>
       </c>
       <c r="AD20" t="n">
         <v>1.048474912581191</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.990578414655753</v>
+        <v>0.9905784146557526</v>
       </c>
       <c r="AF20" t="n">
         <v>0.1656839850212462</v>
@@ -3681,13 +3681,13 @@
         <v>0.1866366616254837</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1242235562921659</v>
+        <v>0.1242235562921657</v>
       </c>
       <c r="AI20" t="n">
         <v>0.8877354726464064</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.333756575375833</v>
+        <v>1.333756575375835</v>
       </c>
       <c r="AK20" t="n">
         <v>6.65529750926154</v>
@@ -3763,7 +3763,7 @@
         <v>44701.55138888889</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>44701.17986111111</v>
+        <v>44701.19583333333</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>44701.38194444445</v>
@@ -3824,22 +3824,22 @@
         <v>68.44135687622847</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.89544014665816</v>
+        <v>94.89544014665815</v>
       </c>
       <c r="AC21" t="n">
-        <v>49.0968373139699</v>
+        <v>49.09683731396996</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.7212291419951721</v>
+        <v>0.7212291419951722</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.394007447741534</v>
+        <v>1.394007447741532</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.3868851761469392</v>
+        <v>0.3868851761469391</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1933988908399361</v>
+        <v>0.1933988908399359</v>
       </c>
       <c r="AH21" t="n">
         <v>0.1698887673936232</v>
@@ -3848,7 +3848,7 @@
         <v>2.000451887116248</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.277285203032565</v>
+        <v>2.277285203032564</v>
       </c>
       <c r="AK21" t="n">
         <v>23.65801058351239</v>
@@ -3924,7 +3924,7 @@
         <v>44746.82083333333</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44744.19583333333</v>
+        <v>44744.25972222222</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>44745.23194444444</v>
@@ -3982,10 +3982,10 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>37.43097229323798</v>
+        <v>37.43097229323799</v>
       </c>
       <c r="AB22" t="n">
-        <v>29.64047508239746</v>
+        <v>29.64047508239747</v>
       </c>
       <c r="AC22" t="n">
         <v>29.34532373348872</v>
@@ -4000,13 +4000,13 @@
         <v>0.3615780958633213</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.1807538486805153</v>
+        <v>0.1807538486805155</v>
       </c>
       <c r="AH22" t="n">
         <v>0.06581203754417686</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.000389471664392</v>
+        <v>2.00038947166439</v>
       </c>
       <c r="AJ22" t="n">
         <v>5.494102741016173</v>
@@ -4562,7 +4562,7 @@
         <v>44803.75763888889</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>44803.28263888889</v>
+        <v>44803.28680555556</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>44803.40763888889</v>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.91999270006289</v>
+        <v>19.9199927000629</v>
       </c>
       <c r="AB26" t="n">
         <v>23.05243274997702</v>
@@ -4629,13 +4629,13 @@
         <v>16.39983092771692</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.864116725384775</v>
+        <v>0.8641167253847755</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.21464622335811</v>
+        <v>1.214646223358111</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.04289823354293122</v>
+        <v>0.04289823354293118</v>
       </c>
       <c r="AG26" t="n">
         <v>0.112592533346274</v>
@@ -4644,10 +4644,10 @@
         <v>0.01798325231930746</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.3810042483989534</v>
+        <v>0.381004248398953</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.385454687574736</v>
+        <v>2.385454687574734</v>
       </c>
       <c r="AK26" t="n">
         <v>4.491017709497143</v>
@@ -5200,7 +5200,7 @@
         <v>44977.25277777778</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>44976.67152777778</v>
+        <v>44976.7</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>44977.01388888889</v>
@@ -5258,7 +5258,7 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>29.79232779316525</v>
+        <v>29.79232779316519</v>
       </c>
       <c r="AB30" t="n">
         <v>32.72847320768566</v>
@@ -5267,25 +5267,25 @@
         <v>17.11524459653425</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.9102877364340077</v>
+        <v>0.9102877364340058</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.740689572102174</v>
+        <v>1.74068957210217</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.5750142379701678</v>
+        <v>0.5750142379701672</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.7930189901429325</v>
+        <v>0.7930189901429311</v>
       </c>
       <c r="AH30" t="n">
         <v>0.1377162112031186</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.7250951681075483</v>
+        <v>0.7250951681075487</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4.175356212218728</v>
+        <v>4.175356212218723</v>
       </c>
       <c r="AK30" t="n">
         <v>5.603413116144038</v>
@@ -5520,7 +5520,7 @@
         <v>44995.36736111111</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>44995.20694444444</v>
+        <v>44995.21597222222</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>44995.30902777778</v>
@@ -5578,25 +5578,25 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>132.8791980599619</v>
+        <v>132.8791980599618</v>
       </c>
       <c r="AB32" t="n">
-        <v>95.94159125523596</v>
+        <v>95.94159125523598</v>
       </c>
       <c r="AC32" t="n">
-        <v>77.20171112114825</v>
+        <v>77.20171112114816</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.385000981549908</v>
+        <v>1.385000981549907</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.721194985580593</v>
+        <v>1.721194985580594</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.9818811067986496</v>
+        <v>0.9818811067986493</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.4830276227527995</v>
+        <v>0.4830276227527994</v>
       </c>
       <c r="AH32" t="n">
         <v>0.4640203595509471</v>
@@ -5605,7 +5605,7 @@
         <v>2.032763884605311</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.116030227097921</v>
+        <v>2.11603022709792</v>
       </c>
       <c r="AK32" t="n">
         <v>37.44234759136311</v>
@@ -5681,7 +5681,7 @@
         <v>45039.49305555555</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45039.25763888889</v>
+        <v>45039.27083333334</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>45039.40972222222</v>
@@ -5754,16 +5754,16 @@
         <v>0.6302897243571223</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.06774094585406019</v>
+        <v>0.06774094585406015</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.09766220330494536</v>
+        <v>0.09766220330494539</v>
       </c>
       <c r="AH33" t="n">
         <v>0.06298208838068024</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.6936250008874207</v>
+        <v>0.6936250008874202</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.075558902471067</v>
@@ -5842,7 +5842,7 @@
         <v>45048.43472222222</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45046.73194444444</v>
+        <v>45046.75555555556</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>45047.25972222222</v>
@@ -5912,7 +5912,7 @@
         <v>1.296623389496918</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.797154066077511</v>
+        <v>1.79715406607751</v>
       </c>
       <c r="AF34" t="n">
         <v>0.08442503516043005</v>
@@ -6003,7 +6003,7 @@
         <v>45058.53402777778</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45057.6375</v>
+        <v>45057.66944444444</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>45058.07013888889</v>
@@ -6026,13 +6026,13 @@
         <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>45057.6375</v>
+        <v>45057.73055555556</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>45057.99027777778</v>
       </c>
       <c r="R35" t="n">
-        <v>508</v>
+        <v>374</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -6061,49 +6061,49 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>9.362221452153895</v>
+        <v>9.936877163486875</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.952951926770417</v>
+        <v>7.51638500318851</v>
       </c>
       <c r="AC35" t="n">
         <v>7.178418268392121</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.368412676296542</v>
+        <v>1.322028762399953</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.304217879498253</v>
+        <v>1.38427112937132</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0823712752101159</v>
+        <v>0.09615287259718039</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.01402628405073308</v>
+        <v>0.03653242051176479</v>
       </c>
       <c r="AH35" t="n">
         <v>0.03269597617287287</v>
       </c>
       <c r="AI35" t="n">
-        <v>5.872637037163866</v>
+        <v>2.631987457995443</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.519309250000541</v>
+        <v>2.940816695265282</v>
       </c>
       <c r="AK35" t="n">
-        <v>9.399903168630471</v>
+        <v>9.062798142403285</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.355806200918353</v>
+        <v>10.39194881046812</v>
       </c>
       <c r="AM35" t="n">
         <v>3.811631670966745</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.801086417343792</v>
+        <v>0.8720980354785871</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.466110049465082</v>
+        <v>2.377668915765065</v>
       </c>
       <c r="AP35" t="n">
         <v>90</v>
@@ -6164,7 +6164,7 @@
         <v>45062.5125</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45061.13125</v>
+        <v>45061.18055555555</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>45061.79652777778</v>
@@ -6180,20 +6180,20 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>最近候选簇内有 3 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>45061.13125</v>
+        <v>45061.61527777778</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>45061.70833333334</v>
+        <v>45061.62430555555</v>
       </c>
       <c r="R36" t="n">
-        <v>831</v>
+        <v>13</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -6213,84 +6213,84 @@
         <v>0</v>
       </c>
       <c r="X36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>19.87848779211263</v>
+        <v>8.620007129815908</v>
       </c>
       <c r="AB36" t="n">
-        <v>7.3199448161655</v>
+        <v>13.12058655288482</v>
       </c>
       <c r="AC36" t="n">
-        <v>17.16904569996729</v>
+        <v>9.143414541085592</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.715660881515475</v>
+        <v>0.6569833669456363</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.15780970820938</v>
+        <v>0.9427558043094544</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.270998704097595</v>
+        <v>0.03011298963159211</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.05610658744940725</v>
+        <v>0.1218339401514193</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.1342492240766932</v>
+        <v>0.02123052516353496</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.830069273807847</v>
+        <v>0.2471642105161065</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.018623988044655</v>
+        <v>1.418381759265826</v>
       </c>
       <c r="AK36" t="n">
-        <v>9.284517587199538</v>
+        <v>4.506142121094924</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.083462710647533</v>
+        <v>10.00695977608363</v>
       </c>
       <c r="AM36" t="n">
-        <v>6.941388326883316</v>
+        <v>7.587345424294472</v>
       </c>
       <c r="AN36" t="n">
-        <v>4.456291701191015</v>
+        <v>0.4503008128267375</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.337559166837204</v>
+        <v>0.5939023293530805</v>
       </c>
       <c r="AP36" t="n">
         <v>100</v>
       </c>
       <c r="AQ36" s="2" t="n">
-        <v>45061.13125</v>
+        <v>45061.61527777778</v>
       </c>
       <c r="AR36" s="2" t="n">
-        <v>45061.64930555555</v>
+        <v>45061.62430555555</v>
       </c>
       <c r="AS36" t="n">
-        <v>746</v>
+        <v>13</v>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="AU36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -6325,7 +6325,7 @@
         <v>45065.17708333334</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45064.28472222222</v>
+        <v>45064.325</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>45064.78263888889</v>
@@ -6386,13 +6386,13 @@
         <v>6.732109641035436</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.922040618651085</v>
+        <v>8.922040618651094</v>
       </c>
       <c r="AC37" t="n">
         <v>7.568758779276203</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.7545481946094589</v>
+        <v>0.7545481946094581</v>
       </c>
       <c r="AE37" t="n">
         <v>0.8894601925309641</v>
@@ -6963,7 +6963,7 @@
         <v>45179.83333333334</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45179.42013888889</v>
+        <v>45179.42847222222</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>45179.56666666667</v>
@@ -6986,13 +6986,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>45179.42013888889</v>
+        <v>45179.42847222222</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>45179.50763888889</v>
+        <v>45179.50277777778</v>
       </c>
       <c r="R41" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -7021,61 +7021,61 @@
         <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>54.58712984014439</v>
+        <v>55.69997336485674</v>
       </c>
       <c r="AB41" t="n">
-        <v>65.58503716256884</v>
+        <v>65.59879712528654</v>
       </c>
       <c r="AC41" t="n">
-        <v>41.8838889731302</v>
+        <v>40.93815042972567</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.8323107251557486</v>
+        <v>0.8491005293660473</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.303296593952001</v>
+        <v>1.360588418875229</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.151515898926488</v>
+        <v>0.1650104340068052</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.2295763882037989</v>
+        <v>0.2251177259506032</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.06283124290602343</v>
+        <v>0.05915081430710085</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.6599803233770918</v>
+        <v>0.7329961837079541</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.411473845155507</v>
+        <v>2.789656168554154</v>
       </c>
       <c r="AK41" t="n">
-        <v>9.8821998720486</v>
+        <v>9.145055284497337</v>
       </c>
       <c r="AL41" t="n">
-        <v>16.48551666736603</v>
+        <v>15.42829785197973</v>
       </c>
       <c r="AM41" t="n">
-        <v>27.67086575031281</v>
+        <v>27.74623583952586</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.5994473859354951</v>
+        <v>0.5927455751914887</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.357133743527229</v>
+        <v>0.3295962500062716</v>
       </c>
       <c r="AP41" t="n">
         <v>100</v>
       </c>
       <c r="AQ41" s="2" t="n">
-        <v>45179.42013888889</v>
+        <v>45179.42847222222</v>
       </c>
       <c r="AR41" s="2" t="n">
-        <v>45179.50763888889</v>
+        <v>45179.50277777778</v>
       </c>
       <c r="AS41" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45228.77916666667</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45227.43819444445</v>
+        <v>45227.45972222222</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>45227.87638888889</v>
@@ -7140,20 +7140,20 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。</t>
         </is>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>45227.43819444445</v>
+        <v>45227.45972222222</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>45227.87638888889</v>
+        <v>45227.73611111111</v>
       </c>
       <c r="R42" t="n">
-        <v>631</v>
+        <v>398</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -7162,15 +7162,15 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>324</v>
+        <v>122</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
@@ -7179,64 +7179,64 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>34.29065320958535</v>
+        <v>38.88639803357128</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.866583710625058</v>
+        <v>18.90727582598934</v>
       </c>
       <c r="AC42" t="n">
-        <v>12.09299057987003</v>
+        <v>25.05546454323663</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.867403086545494</v>
+        <v>2.056689625277443</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.8355809080564</v>
+        <v>1.552012654423847</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.2206102735744261</v>
+        <v>0.3094664520228259</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.04369823574993836</v>
+        <v>0.1544505029921034</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.008494194701990901</v>
+        <v>0.01249091574570305</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.048493830205429</v>
+        <v>2.003661017786702</v>
       </c>
       <c r="AJ42" t="n">
-        <v>25.97188801461293</v>
+        <v>24.77532138740782</v>
       </c>
       <c r="AK42" t="n">
-        <v>28.49744627494867</v>
+        <v>28.12759910091458</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.525554111805455</v>
+        <v>11.22223939052943</v>
       </c>
       <c r="AM42" t="n">
-        <v>19.30856167078018</v>
+        <v>31.52770136197408</v>
       </c>
       <c r="AN42" t="n">
-        <v>4.367053860360089</v>
+        <v>2.506415887425442</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.475896898010488</v>
+        <v>0.8921550853954612</v>
       </c>
       <c r="AP42" t="n">
         <v>95.83333333333334</v>
       </c>
       <c r="AQ42" s="2" t="n">
-        <v>45227.43819444445</v>
+        <v>45227.45972222222</v>
       </c>
       <c r="AR42" s="2" t="n">
-        <v>45227.87638888889</v>
+        <v>45227.66111111111</v>
       </c>
       <c r="AS42" t="n">
-        <v>631</v>
+        <v>290</v>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45234.14930555555</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45232.45208333333</v>
+        <v>45232.53541666667</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>45233.45486111111</v>
@@ -7301,7 +7301,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。最近候选簇内有 17 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>检测到 3 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。最近候选簇内有 17 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -7446,7 +7446,7 @@
         <v>45235.11527777778</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45234.39583333334</v>
+        <v>45234.42569444444</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>45234.77847222222</v>
@@ -7469,13 +7469,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>45234.39583333334</v>
+        <v>45234.42569444444</v>
       </c>
       <c r="Q44" s="2" t="n">
         <v>45234.61597222222</v>
       </c>
       <c r="R44" t="n">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="S44" t="n">
         <v>113</v>
@@ -7504,49 +7504,49 @@
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>26.4760677355697</v>
+        <v>27.81876290743658</v>
       </c>
       <c r="AB44" t="n">
-        <v>6.137672368354268</v>
+        <v>11.09743559658527</v>
       </c>
       <c r="AC44" t="n">
         <v>23.58100073287885</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.313698442438838</v>
+        <v>2.506773989839286</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.122771168004515</v>
+        <v>1.179710870737095</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.6848820725526672</v>
+        <v>0.7664793353169554</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.09803095812336306</v>
+        <v>0.147247114237936</v>
       </c>
       <c r="AH44" t="n">
         <v>0.1174999152948415</v>
       </c>
       <c r="AI44" t="n">
-        <v>6.98638558332568</v>
+        <v>5.205394613563731</v>
       </c>
       <c r="AJ44" t="n">
-        <v>5.828787798136696</v>
+        <v>6.523233088242113</v>
       </c>
       <c r="AK44" t="n">
-        <v>12.93884729373942</v>
+        <v>13.68196705494919</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.659848321663837</v>
+        <v>5.271718565832513</v>
       </c>
       <c r="AM44" t="n">
         <v>16.3086303587382</v>
       </c>
       <c r="AN44" t="n">
-        <v>4.864505689424303</v>
+        <v>2.595352328484653</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.7933742447480729</v>
+        <v>0.8389402883006886</v>
       </c>
       <c r="AP44" t="n">
         <v>90</v>
@@ -7607,7 +7607,7 @@
         <v>45251.08263888889</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45250.45972222222</v>
+        <v>45250.48888888889</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>45250.81597222222</v>
@@ -7768,7 +7768,7 @@
         <v>45253.94930555556</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45253.16111111111</v>
+        <v>45253.18680555555</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>45253.52013888889</v>
@@ -7791,13 +7791,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>45253.16111111111</v>
+        <v>45253.18680555555</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>45253.52013888889</v>
       </c>
       <c r="R46" t="n">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7826,61 +7826,61 @@
         <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>13.03255549281143</v>
+        <v>13.35874582415417</v>
       </c>
       <c r="AB46" t="n">
-        <v>3.956116382906466</v>
+        <v>5.638342584504021</v>
       </c>
       <c r="AC46" t="n">
-        <v>15.00135223600602</v>
+        <v>15.00135223600603</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.294280104883242</v>
+        <v>2.36926820673655</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.8687587150664245</v>
+        <v>0.890502776949047</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.1149111625272737</v>
+        <v>0.1215025499821889</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.01272486294713705</v>
+        <v>0.01908658990530727</v>
       </c>
       <c r="AH46" t="n">
         <v>0.02313257181833788</v>
       </c>
       <c r="AI46" t="n">
-        <v>9.030444021648762</v>
+        <v>6.36585951628811</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.967504842508697</v>
+        <v>5.25244451573993</v>
       </c>
       <c r="AK46" t="n">
-        <v>16.6848240383762</v>
+        <v>16.39451122541601</v>
       </c>
       <c r="AL46" t="n">
-        <v>9.041696726282437</v>
+        <v>13.22235392729441</v>
       </c>
       <c r="AM46" t="n">
         <v>6.04439692273736</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.845320026038552</v>
+        <v>1.239908666457145</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.760378620340513</v>
+        <v>2.712348549405213</v>
       </c>
       <c r="AP46" t="n">
-        <v>90</v>
+        <v>99.79166666666667</v>
       </c>
       <c r="AQ46" s="2" t="n">
-        <v>45253.16111111111</v>
+        <v>45253.18680555555</v>
       </c>
       <c r="AR46" s="2" t="n">
         <v>45253.52013888889</v>
       </c>
       <c r="AS46" t="n">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45301.62708333333</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45301.42569444444</v>
+        <v>45301.43402777778</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>45301.52708333333</v>
@@ -8270,13 +8270,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>45301.42569444444</v>
+        <v>45301.43541666667</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>45301.51180555556</v>
+        <v>45301.51527777778</v>
       </c>
       <c r="R49" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -8305,61 +8305,61 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>41.13004656904558</v>
+        <v>40.54292987992866</v>
       </c>
       <c r="AB49" t="n">
-        <v>23.57764967575506</v>
+        <v>25.6991356491452</v>
       </c>
       <c r="AC49" t="n">
-        <v>21.67687946816343</v>
+        <v>21.38997688775807</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.744450661311661</v>
+        <v>1.577598968052343</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.897415475758528</v>
+        <v>1.895417189680659</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1892485605994413</v>
+        <v>0.195821040341589</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.09440372774669824</v>
+        <v>0.09759758418567627</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.06942270387627782</v>
+        <v>0.06974331147285155</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.004672539067826</v>
+        <v>2.006412781376286</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.726032695826888</v>
+        <v>2.80773935458764</v>
       </c>
       <c r="AK49" t="n">
-        <v>16.36976588156915</v>
+        <v>15.95148381564928</v>
       </c>
       <c r="AL49" t="n">
-        <v>7.233458983401458</v>
+        <v>8.48150582263867</v>
       </c>
       <c r="AM49" t="n">
-        <v>19.83972006440163</v>
+        <v>20.26715065638224</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.263061962351993</v>
+        <v>1.880737235724332</v>
       </c>
       <c r="AO49" t="n">
-        <v>0.8251006480147569</v>
+        <v>0.7870609976753722</v>
       </c>
       <c r="AP49" t="n">
         <v>100</v>
       </c>
       <c r="AQ49" s="2" t="n">
-        <v>45301.42569444444</v>
+        <v>45301.43541666667</v>
       </c>
       <c r="AR49" s="2" t="n">
-        <v>45301.51180555556</v>
+        <v>45301.51527777778</v>
       </c>
       <c r="AS49" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45314.97916666666</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45314.04305555556</v>
+        <v>45314.04652777778</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>45314.25277777778</v>
@@ -8790,13 +8790,13 @@
         <v>32.98351290103364</v>
       </c>
       <c r="AC52" t="n">
-        <v>34.15342914886641</v>
+        <v>34.15342914886639</v>
       </c>
       <c r="AD52" t="n">
         <v>0.7148967006780511</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.6904081123726202</v>
+        <v>0.6904081123726206</v>
       </c>
       <c r="AF52" t="n">
         <v>0.07542901876718133</v>
@@ -8887,7 +8887,7 @@
         <v>45330.57916666667</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45330.18472222222</v>
+        <v>45330.19652777778</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>45330.35763888889</v>
@@ -8910,13 +8910,13 @@
         <v>1</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>45330.18472222222</v>
+        <v>45330.24583333333</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>45330.31736111111</v>
+        <v>45330.35763888889</v>
       </c>
       <c r="R53" t="n">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -8925,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -8936,70 +8936,70 @@
         <v>0</v>
       </c>
       <c r="X53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>41.34325206217341</v>
+        <v>40.41393914627486</v>
       </c>
       <c r="AB53" t="n">
-        <v>11.86307403776381</v>
+        <v>34.87600541777081</v>
       </c>
       <c r="AC53" t="n">
-        <v>42.20547906557719</v>
+        <v>38.64341987503899</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.485037009005014</v>
+        <v>1.158789220903213</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.9795707329357859</v>
+        <v>1.045816837043957</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.020327880728837</v>
+        <v>1.961429316620686</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.508056095015834</v>
+        <v>3.043787086469977</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.50898592113993</v>
+        <v>0.2608966720554359</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.002795446874357</v>
+        <v>0.644404244087732</v>
       </c>
       <c r="AJ53" t="n">
-        <v>5.934010657828177</v>
+        <v>7.518031185173252</v>
       </c>
       <c r="AK53" t="n">
-        <v>10.86310986058874</v>
+        <v>6.969881913769319</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.122345913207391</v>
+        <v>11.86344811879098</v>
       </c>
       <c r="AM53" t="n">
-        <v>8.008896504715086</v>
+        <v>11.65814435730378</v>
       </c>
       <c r="AN53" t="n">
-        <v>5.118444544307054</v>
+        <v>0.587508947144081</v>
       </c>
       <c r="AO53" t="n">
-        <v>1.356380352048911</v>
+        <v>0.5978551731865216</v>
       </c>
       <c r="AP53" t="n">
         <v>100</v>
       </c>
       <c r="AQ53" s="2" t="n">
-        <v>45330.18472222222</v>
+        <v>45330.24583333333</v>
       </c>
       <c r="AR53" s="2" t="n">
-        <v>45330.31736111111</v>
+        <v>45330.35763888889</v>
       </c>
       <c r="AS53" t="n">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
@@ -9010,10 +9010,10 @@
         <v>0</v>
       </c>
       <c r="AV53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -9048,7 +9048,7 @@
         <v>45330.80555555555</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45330.71180555555</v>
+        <v>45330.71388888889</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>45330.74166666667</v>
@@ -9071,13 +9071,13 @@
         <v>1</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>45330.71180555555</v>
+        <v>45330.71388888889</v>
       </c>
       <c r="Q54" s="2" t="n">
         <v>45330.72777777778</v>
       </c>
       <c r="R54" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -9106,61 +9106,61 @@
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>51.88073167656409</v>
+        <v>52.00546235368964</v>
       </c>
       <c r="AB54" t="n">
-        <v>51.84165736725835</v>
+        <v>51.91831711891924</v>
       </c>
       <c r="AC54" t="n">
-        <v>17.99859174593489</v>
+        <v>17.9985917459349</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.000753724153318</v>
+        <v>1.001678506538854</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.882488386252871</v>
+        <v>2.889418410495112</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.3130755982141867</v>
+        <v>0.3044086485440246</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.012946754271655</v>
+        <v>1.004671281897757</v>
       </c>
       <c r="AH54" t="n">
         <v>0.1099420986685051</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.3090740918946913</v>
+        <v>0.3029932815129512</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.847640730946615</v>
+        <v>2.768808784175301</v>
       </c>
       <c r="AK54" t="n">
-        <v>10.18237671644791</v>
+        <v>10.14512174129486</v>
       </c>
       <c r="AL54" t="n">
-        <v>18.04479331349333</v>
+        <v>17.92890045021971</v>
       </c>
       <c r="AM54" t="n">
         <v>41.22409843405088</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.5642833663732713</v>
+        <v>0.565852979632699</v>
       </c>
       <c r="AO54" t="n">
-        <v>0.2470005919653376</v>
+        <v>0.2460968735926326</v>
       </c>
       <c r="AP54" t="n">
         <v>91.66666666666666</v>
       </c>
       <c r="AQ54" s="2" t="n">
-        <v>45330.71180555555</v>
+        <v>45330.71388888889</v>
       </c>
       <c r="AR54" s="2" t="n">
         <v>45330.72777777778</v>
       </c>
       <c r="AS54" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45339.35902777778</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45338.18194444444</v>
+        <v>45338.23680555556</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>45338.85138888889</v>
@@ -9429,13 +9429,13 @@
         <v>12.95943466484126</v>
       </c>
       <c r="AB56" t="n">
-        <v>23.17342201348957</v>
+        <v>23.17342201348961</v>
       </c>
       <c r="AC56" t="n">
         <v>17.20669034322103</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.5592369852539429</v>
+        <v>0.5592369852539422</v>
       </c>
       <c r="AE56" t="n">
         <v>0.7531625435420781</v>
@@ -9529,7 +9529,7 @@
         <v>45358.575</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45357.54166666666</v>
+        <v>45357.59236111111</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>45358.15</v>
@@ -9587,31 +9587,31 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>22.66882199309335</v>
+        <v>22.66882199309336</v>
       </c>
       <c r="AB57" t="n">
-        <v>15.30791553318676</v>
+        <v>15.30791553318677</v>
       </c>
       <c r="AC57" t="n">
         <v>11.16798492802509</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.48085622395476</v>
+        <v>1.480856223954759</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.02980413558832</v>
+        <v>2.029804135588321</v>
       </c>
       <c r="AF57" t="n">
         <v>0.2379749417825176</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.1174857789026333</v>
+        <v>0.117485778902633</v>
       </c>
       <c r="AH57" t="n">
         <v>0.01967844896694449</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.025563808703521</v>
+        <v>2.025563808703526</v>
       </c>
       <c r="AJ57" t="n">
         <v>12.09317574684182</v>
@@ -9690,7 +9690,7 @@
         <v>45364.08263888889</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45363.46597222222</v>
+        <v>45363.48333333333</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>45363.72638888889</v>
@@ -9713,13 +9713,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>45363.46597222222</v>
+        <v>45363.48333333333</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>45363.64097222222</v>
+        <v>45363.64305555556</v>
       </c>
       <c r="R58" t="n">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -9748,61 +9748,61 @@
         <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>72.60807811267793</v>
+        <v>73.86521527387096</v>
       </c>
       <c r="AB58" t="n">
-        <v>26.77339777681563</v>
+        <v>33.86758876111772</v>
       </c>
       <c r="AC58" t="n">
-        <v>91.41965114275621</v>
+        <v>91.1502774238587</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.711948581123041</v>
+        <v>2.181000123595253</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.7942283437430416</v>
+        <v>0.8103674213781016</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.3241945063130456</v>
+        <v>0.32813372873346</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.1049516056077635</v>
+        <v>0.1351242266938826</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.1617823824772735</v>
+        <v>0.1636219252318803</v>
       </c>
       <c r="AI58" t="n">
-        <v>3.088990439314101</v>
+        <v>2.428385617901304</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.003892521230407</v>
+        <v>2.005438624856897</v>
       </c>
       <c r="AK58" t="n">
-        <v>39.51352856414659</v>
+        <v>39.21632598949515</v>
       </c>
       <c r="AL58" t="n">
-        <v>15.08720228224993</v>
+        <v>21.99794828891754</v>
       </c>
       <c r="AM58" t="n">
-        <v>41.60265514055888</v>
+        <v>41.53127687772115</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.619009662953495</v>
+        <v>1.782726528603222</v>
       </c>
       <c r="AO58" t="n">
-        <v>0.9497838162166823</v>
+        <v>0.9442600598329348</v>
       </c>
       <c r="AP58" t="n">
         <v>100</v>
       </c>
       <c r="AQ58" s="2" t="n">
-        <v>45363.46597222222</v>
+        <v>45363.48333333333</v>
       </c>
       <c r="AR58" s="2" t="n">
-        <v>45363.64097222222</v>
+        <v>45363.64305555556</v>
       </c>
       <c r="AS58" t="n">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45366.64444444444</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45365.90486111111</v>
+        <v>45365.93055555555</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>45366.25625</v>
@@ -9912,7 +9912,7 @@
         <v>31.88129475911465</v>
       </c>
       <c r="AB59" t="n">
-        <v>30.15932253201802</v>
+        <v>30.15932253201803</v>
       </c>
       <c r="AC59" t="n">
         <v>27.65052752229904</v>
@@ -9927,16 +9927,16 @@
         <v>0.1749261230670641</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.08508198730616595</v>
+        <v>0.08508198730616613</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.08715453114692935</v>
+        <v>0.0871545311469295</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.055971288465509</v>
+        <v>2.055971288465504</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.007080076791017</v>
+        <v>2.007080076791014</v>
       </c>
       <c r="AK59" t="n">
         <v>24.11812210083008</v>
@@ -10489,7 +10489,7 @@
         <v>45375.99305555555</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45375.56111111111</v>
+        <v>45375.57083333333</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>45375.72083333333</v>
@@ -10553,28 +10553,28 @@
         <v>34.34198532760034</v>
       </c>
       <c r="AC63" t="n">
-        <v>45.18932556290811</v>
+        <v>45.18932556290807</v>
       </c>
       <c r="AD63" t="n">
         <v>1.168034904209702</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.8876573625037583</v>
+        <v>0.8876573625037589</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.1274110935583047</v>
+        <v>0.1274110935583049</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.0724330205810034</v>
+        <v>0.07243302058100337</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.07422583950674587</v>
+        <v>0.07422583950674592</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.759019471179145</v>
+        <v>1.759019471179148</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.716532873255347</v>
+        <v>1.716532873255348</v>
       </c>
       <c r="AK63" t="n">
         <v>19.10166546132635</v>
@@ -10650,7 +10650,7 @@
         <v>45390.65486111111</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45390.38541666666</v>
+        <v>45390.40347222222</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>45390.57986111111</v>
@@ -10711,13 +10711,13 @@
         <v>55.33165461222306</v>
       </c>
       <c r="AB64" t="n">
-        <v>48.99735986921528</v>
+        <v>48.99735986921522</v>
       </c>
       <c r="AC64" t="n">
         <v>46.07067912684552</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.129278286828421</v>
+        <v>1.129278286828423</v>
       </c>
       <c r="AE64" t="n">
         <v>1.201016691329413</v>
@@ -10726,13 +10726,13 @@
         <v>0.7994973964821839</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.396246512084835</v>
+        <v>0.3962465120848321</v>
       </c>
       <c r="AH64" t="n">
         <v>0.3363197239349536</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.01767680496583</v>
+        <v>2.017676804965844</v>
       </c>
       <c r="AJ64" t="n">
         <v>2.377194495547373</v>
@@ -11288,7 +11288,7 @@
         <v>45426.98611111111</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45426.77847222222</v>
+        <v>45426.78680555556</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>45426.88263888889</v>
@@ -11449,7 +11449,7 @@
         <v>45481.20625</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45480.56875</v>
+        <v>45480.57986111111</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>45480.78263888889</v>
@@ -11507,7 +11507,7 @@
         <v>1</v>
       </c>
       <c r="AA69" t="n">
-        <v>49.93976842201405</v>
+        <v>49.93976842201398</v>
       </c>
       <c r="AB69" t="n">
         <v>52.12903743528223</v>
@@ -11516,25 +11516,25 @@
         <v>47.08807265256976</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.9580028881986142</v>
+        <v>0.9580028881986128</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.060560893848533</v>
+        <v>1.060560893848532</v>
       </c>
       <c r="AF69" t="n">
-        <v>0.07027695834037814</v>
+        <v>0.07027695834037828</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.1994447401716486</v>
+        <v>0.1994447401716485</v>
       </c>
       <c r="AH69" t="n">
         <v>0.08111668691955233</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.3523630569545004</v>
+        <v>0.3523630569545013</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.8663686968635133</v>
+        <v>0.8663686968635149</v>
       </c>
       <c r="AK69" t="n">
         <v>6.851785252690315</v>
@@ -11610,7 +11610,7 @@
         <v>45502.58958333333</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45502.04236111111</v>
+        <v>45502.06111111111</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>45502.29652777778</v>
@@ -11633,13 +11633,13 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>45502.04236111111</v>
+        <v>45502.06111111111</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>45502.29652777778</v>
       </c>
       <c r="R70" t="n">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -11668,61 +11668,61 @@
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>36.51242626516762</v>
+        <v>36.35265205930936</v>
       </c>
       <c r="AB70" t="n">
-        <v>13.46297639475928</v>
+        <v>19.21962988773982</v>
       </c>
       <c r="AC70" t="n">
         <v>23.89214664035376</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.712061968658043</v>
+        <v>1.891433512072919</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.528218741278703</v>
+        <v>1.521531430663072</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.8631149449844607</v>
+        <v>0.894280264096968</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.2344049830118878</v>
+        <v>0.2847756773600778</v>
       </c>
       <c r="AH70" t="n">
         <v>0.1051613587522373</v>
       </c>
       <c r="AI70" t="n">
-        <v>3.682152716611353</v>
+        <v>3.140297206513943</v>
       </c>
       <c r="AJ70" t="n">
-        <v>8.207529412186281</v>
+        <v>8.503886548327261</v>
       </c>
       <c r="AK70" t="n">
-        <v>11.53929877496844</v>
+        <v>11.14102082358739</v>
       </c>
       <c r="AL70" t="n">
-        <v>7.76766470024983</v>
+        <v>10.60070094068845</v>
       </c>
       <c r="AM70" t="n">
         <v>6.531102759685989</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.485555726239998</v>
+        <v>1.050970203378254</v>
       </c>
       <c r="AO70" t="n">
-        <v>1.766822418749271</v>
+        <v>1.705840687786552</v>
       </c>
       <c r="AP70" t="n">
         <v>100</v>
       </c>
       <c r="AQ70" s="2" t="n">
-        <v>45502.04236111111</v>
+        <v>45502.06111111111</v>
       </c>
       <c r="AR70" s="2" t="n">
         <v>45502.29652777778</v>
       </c>
       <c r="AS70" t="n">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45514.08333333334</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45513.49375</v>
+        <v>45513.50694444445</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>45513.71388888889</v>
@@ -12105,20 +12105,20 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>45513.49375</v>
+        <v>45513.50694444445</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>45513.68194444444</v>
+        <v>45513.66736111111</v>
       </c>
       <c r="R73" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -12147,61 +12147,61 @@
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>14.01331357791708</v>
+        <v>14.14729270756158</v>
       </c>
       <c r="AB73" t="n">
-        <v>4.757953766404395</v>
+        <v>6.614028686471815</v>
       </c>
       <c r="AC73" t="n">
-        <v>10.15153744419415</v>
+        <v>10.08939106927977</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.945239543281018</v>
+        <v>2.138982665209502</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.380412933011595</v>
+        <v>1.40219490060578</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.1642902072294588</v>
+        <v>0.1627065175153745</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.03890358107808174</v>
+        <v>0.07652426810665362</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.08152880071882755</v>
+        <v>0.08111072565580849</v>
       </c>
       <c r="AI73" t="n">
-        <v>4.223009879211861</v>
+        <v>2.126208084585751</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.015118654769063</v>
+        <v>2.005980296685002</v>
       </c>
       <c r="AK73" t="n">
-        <v>12.71923706188413</v>
+        <v>13.37269592904425</v>
       </c>
       <c r="AL73" t="n">
-        <v>5.462894686559836</v>
+        <v>5.543857849140962</v>
       </c>
       <c r="AM73" t="n">
-        <v>11.60357647736867</v>
+        <v>10.87609403928121</v>
       </c>
       <c r="AN73" t="n">
-        <v>2.328296222362993</v>
+        <v>2.412164289370514</v>
       </c>
       <c r="AO73" t="n">
-        <v>1.096147992534148</v>
+        <v>1.229549494583815</v>
       </c>
       <c r="AP73" t="n">
         <v>97.5</v>
       </c>
       <c r="AQ73" s="2" t="n">
-        <v>45513.49375</v>
+        <v>45513.50694444445</v>
       </c>
       <c r="AR73" s="2" t="n">
-        <v>45513.68194444444</v>
+        <v>45513.66736111111</v>
       </c>
       <c r="AS73" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45518.84027777778</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45517.62291666667</v>
+        <v>45517.66180555556</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>45518.17222222222</v>
@@ -13061,7 +13061,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -13106,13 +13106,13 @@
         <v>7.514529109199346</v>
       </c>
       <c r="AB79" t="n">
-        <v>8.680528563923305</v>
+        <v>8.680528563923307</v>
       </c>
       <c r="AC79" t="n">
         <v>4.073955761180026</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.8656764451452981</v>
+        <v>0.8656764451452978</v>
       </c>
       <c r="AE79" t="n">
         <v>1.844528892729742</v>
@@ -13121,13 +13121,13 @@
         <v>0.02904451822871161</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.03824135517116979</v>
+        <v>0.03824135517116977</v>
       </c>
       <c r="AH79" t="n">
         <v>0.004940443688064329</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.75950546466534</v>
+        <v>0.7595054646653404</v>
       </c>
       <c r="AJ79" t="n">
         <v>5.878929112962178</v>
@@ -13206,7 +13206,7 @@
         <v>45531.65625</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45530.10694444444</v>
+        <v>45530.14930555555</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>45530.75069444445</v>
@@ -13229,13 +13229,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>45530.10694444444</v>
+        <v>45530.14930555555</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>45530.575</v>
       </c>
       <c r="R80" t="n">
-        <v>674</v>
+        <v>613</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -13248,11 +13248,11 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X80" t="b">
         <v>1</v>
@@ -13261,52 +13261,52 @@
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA80" t="n">
-        <v>54.97466221572618</v>
+        <v>55.81432672711153</v>
       </c>
       <c r="AB80" t="n">
-        <v>10.36087493535244</v>
+        <v>29.02386278377639</v>
       </c>
       <c r="AC80" t="n">
         <v>21.72487735895461</v>
       </c>
       <c r="AD80" t="n">
-        <v>5.305986469168411</v>
+        <v>1.923049565901005</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.530493558485687</v>
+        <v>2.569143466492613</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.2965427208596387</v>
+        <v>0.3090884831913622</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.009910918257933559</v>
+        <v>0.09237027204197243</v>
       </c>
       <c r="AH80" t="n">
         <v>0.01264536794778126</v>
       </c>
       <c r="AI80" t="n">
-        <v>29.92081189069036</v>
+        <v>3.346190028009384</v>
       </c>
       <c r="AJ80" t="n">
-        <v>23.45069926665673</v>
+        <v>24.44282242064726</v>
       </c>
       <c r="AK80" t="n">
-        <v>14.0293639145062</v>
+        <v>14.94129525171213</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.044588477847477</v>
+        <v>3.481731870460014</v>
       </c>
       <c r="AM80" t="n">
         <v>13.35712289810181</v>
       </c>
       <c r="AN80" t="n">
-        <v>6.86170545638415</v>
+        <v>4.291340001933594</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.050328279640215</v>
+        <v>1.118601315994139</v>
       </c>
       <c r="AP80" t="n">
         <v>90</v>
@@ -13367,7 +13367,7 @@
         <v>45537.33888888889</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45536.72708333333</v>
+        <v>45536.75694444445</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>45537.0875</v>
@@ -13428,13 +13428,13 @@
         <v>35.2782562650909</v>
       </c>
       <c r="AB81" t="n">
-        <v>24.6044774108463</v>
+        <v>24.60447741084629</v>
       </c>
       <c r="AC81" t="n">
         <v>26.64577882024975</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.433814491403882</v>
+        <v>1.433814491403883</v>
       </c>
       <c r="AE81" t="n">
         <v>1.323971669324254</v>
@@ -13443,16 +13443,16 @@
         <v>0.2445384147437047</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.08754144215581669</v>
+        <v>0.08754144215581663</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.1222620553851449</v>
+        <v>0.1222620553851448</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.793401716051766</v>
+        <v>2.793401716051768</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.000116994380389</v>
+        <v>2.000116994380391</v>
       </c>
       <c r="AK81" t="n">
         <v>9.880248594631269</v>
@@ -13528,7 +13528,7 @@
         <v>45545.07152777778</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45544.85416666666</v>
+        <v>45544.86597222222</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>45544.99027777778</v>
@@ -13589,28 +13589,28 @@
         <v>26.87514540982343</v>
       </c>
       <c r="AB82" t="n">
-        <v>26.91856260697047</v>
+        <v>26.91856260697046</v>
       </c>
       <c r="AC82" t="n">
-        <v>25.95298853980171</v>
+        <v>25.95298853980172</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.998387090804923</v>
+        <v>0.9983870908049233</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.035531818179918</v>
+        <v>1.035531818179917</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.2925863867586581</v>
+        <v>0.292586386758658</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.2248850349124017</v>
+        <v>0.2248850349124018</v>
       </c>
       <c r="AH82" t="n">
         <v>0.2065823617818739</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.301048719727516</v>
+        <v>1.301048719727515</v>
       </c>
       <c r="AJ82" t="n">
         <v>1.416318335384286</v>
@@ -13689,7 +13689,7 @@
         <v>45545.80555555555</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45545.58611111111</v>
+        <v>45545.59444444445</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>45545.69652777778</v>
@@ -13753,28 +13753,28 @@
         <v>30.15047423839569</v>
       </c>
       <c r="AC83" t="n">
-        <v>20.58798242674934</v>
+        <v>20.58798242674932</v>
       </c>
       <c r="AD83" t="n">
         <v>1.109356656259397</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.624619090517788</v>
+        <v>1.62461909051779</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.1265864060263719</v>
+        <v>0.1265864060263721</v>
       </c>
       <c r="AG83" t="n">
         <v>0.128576521134838</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.06373139245431644</v>
+        <v>0.06373139245431651</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.9845219400019454</v>
+        <v>0.9845219400019473</v>
       </c>
       <c r="AJ83" t="n">
-        <v>1.986248866555219</v>
+        <v>1.98624886655522</v>
       </c>
       <c r="AK83" t="n">
         <v>12.73120430707931</v>
@@ -13850,7 +13850,7 @@
         <v>45546.31944444445</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45546.07361111111</v>
+        <v>45546.08333333334</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>45546.19652777778</v>
@@ -13911,7 +13911,7 @@
         <v>26.29401111602783</v>
       </c>
       <c r="AB84" t="n">
-        <v>22.42013194627231</v>
+        <v>22.42013194627232</v>
       </c>
       <c r="AC84" t="n">
         <v>21.5345012747607</v>
@@ -13923,7 +13923,7 @@
         <v>1.221017881052368</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.4320722829102792</v>
+        <v>0.4320722829102784</v>
       </c>
       <c r="AG84" t="n">
         <v>0.1706772021345549</v>
@@ -13932,10 +13932,10 @@
         <v>0.2099942281985546</v>
       </c>
       <c r="AI84" t="n">
-        <v>2.531517258934507</v>
+        <v>2.531517258934502</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.057543612587982</v>
+        <v>2.057543612587979</v>
       </c>
       <c r="AK84" t="n">
         <v>26.48758316040039</v>
@@ -14011,7 +14011,7 @@
         <v>45550.8125</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45550.60555555556</v>
+        <v>45550.61458333334</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>45550.71597222222</v>
@@ -14072,7 +14072,7 @@
         <v>47.47740898132324</v>
       </c>
       <c r="AB85" t="n">
-        <v>44.15814772310916</v>
+        <v>44.15814772310915</v>
       </c>
       <c r="AC85" t="n">
         <v>40.92495942645601</v>
@@ -14090,13 +14090,13 @@
         <v>0.667501909081429</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.5132712153154959</v>
+        <v>0.5132712153154954</v>
       </c>
       <c r="AI85" t="n">
         <v>1.125416719203624</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1.463588422972095</v>
+        <v>1.463588422972096</v>
       </c>
       <c r="AK85" t="n">
         <v>11.13141592144966</v>
@@ -14172,7 +14172,7 @@
         <v>45569.2625</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45569.01180555556</v>
+        <v>45569.02638888889</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>45569.17569444444</v>
@@ -14188,7 +14188,7 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 4 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -14239,7 +14239,7 @@
         <v>196.5667760555084</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.8849045374310919</v>
+        <v>0.8849045374310918</v>
       </c>
       <c r="AE86" t="n">
         <v>1.563535626845439</v>
@@ -14333,7 +14333,7 @@
         <v>45648.45277777778</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45648.25625</v>
+        <v>45648.26319444444</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>45648.34722222222</v>
@@ -14394,7 +14394,7 @@
         <v>1071.811593427947</v>
       </c>
       <c r="AB87" t="n">
-        <v>769.0270869136625</v>
+        <v>769.0270869136624</v>
       </c>
       <c r="AC87" t="n">
         <v>1186.699336181883</v>
@@ -14403,22 +14403,22 @@
         <v>1.3937241114997</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.9031871517484965</v>
+        <v>0.903187151748497</v>
       </c>
       <c r="AF87" t="n">
         <v>0.1215905253965301</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.07030967246683018</v>
+        <v>0.07030967246683013</v>
       </c>
       <c r="AH87" t="n">
         <v>0.1276637507993103</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.729357016332178</v>
+        <v>1.729357016332179</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.9524279573116462</v>
+        <v>0.9524279573116463</v>
       </c>
       <c r="AK87" t="n">
         <v>52.60046935081482</v>
@@ -14494,7 +14494,7 @@
         <v>45680.11041666667</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45679.82083333333</v>
+        <v>45679.83125</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>45679.96111111111</v>
@@ -14552,31 +14552,31 @@
         <v>1</v>
       </c>
       <c r="AA88" t="n">
-        <v>133.7435233857896</v>
+        <v>133.7435233857897</v>
       </c>
       <c r="AB88" t="n">
         <v>45.07509667343564</v>
       </c>
       <c r="AC88" t="n">
-        <v>66.63451621267535</v>
+        <v>66.63451621267532</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.96712671200125</v>
+        <v>2.967126712001253</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.007120798460132</v>
+        <v>2.007120798460135</v>
       </c>
       <c r="AF88" t="n">
         <v>0.3021731374543085</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.6483424186047962</v>
+        <v>0.6483424186047961</v>
       </c>
       <c r="AH88" t="n">
         <v>0.9266960551597211</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.4660702875257977</v>
+        <v>0.4660702875257978</v>
       </c>
       <c r="AJ88" t="n">
         <v>0.3260757783221893</v>
@@ -14655,7 +14655,7 @@
         <v>45680.74444444444</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45680.13611111111</v>
+        <v>45680.14166666667</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>45680.29791666667</v>
@@ -14731,16 +14731,16 @@
         <v>0.9036845172775647</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.4494906391892233</v>
+        <v>0.4494906391892232</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.2144002117014117</v>
+        <v>0.2144002117014115</v>
       </c>
       <c r="AI89" t="n">
-        <v>2.010463485752677</v>
+        <v>2.010463485752678</v>
       </c>
       <c r="AJ89" t="n">
-        <v>4.214942280635885</v>
+        <v>4.214942280635888</v>
       </c>
       <c r="AK89" t="n">
         <v>8.317249683233408</v>
@@ -14816,7 +14816,7 @@
         <v>45694.08541666667</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45692.34375</v>
+        <v>45692.41041666667</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>45693.22083333333</v>
@@ -14874,7 +14874,7 @@
         <v>1</v>
       </c>
       <c r="AA90" t="n">
-        <v>20.54612173841565</v>
+        <v>20.54612173841566</v>
       </c>
       <c r="AB90" t="n">
         <v>29.26155734945226</v>
@@ -14883,22 +14883,22 @@
         <v>14.89722646394018</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.7021540751589646</v>
+        <v>0.7021540751589649</v>
       </c>
       <c r="AE90" t="n">
         <v>1.37919107211997</v>
       </c>
       <c r="AF90" t="n">
-        <v>0.8330392202328561</v>
+        <v>0.833039220232856</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.4164978987508677</v>
+        <v>0.4164978987508678</v>
       </c>
       <c r="AH90" t="n">
         <v>0.0472008830237557</v>
       </c>
       <c r="AI90" t="n">
-        <v>2.00010425678317</v>
+        <v>2.000104256783169</v>
       </c>
       <c r="AJ90" t="n">
         <v>17.64880584572107</v>
@@ -14977,7 +14977,7 @@
         <v>45773.41458333333</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45773.07152777778</v>
+        <v>45773.07916666667</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>45773.19583333333</v>
@@ -15056,13 +15056,13 @@
         <v>0.2645917149558492</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.1930458629036919</v>
+        <v>0.193045862903692</v>
       </c>
       <c r="AI91" t="n">
-        <v>2.000003216499575</v>
+        <v>2.000003216499574</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.741236061789318</v>
+        <v>2.741236061789316</v>
       </c>
       <c r="AK91" t="n">
         <v>13.10814215435136</v>
@@ -15672,7 +15672,7 @@
         <v>44670.44791666666</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>44669.8625</v>
+        <v>44669.88402777778</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>44670.14652777778</v>
@@ -15765,7 +15765,7 @@
         <v>44694.88541666666</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44694.54513888889</v>
+        <v>44694.5625</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>44694.74861111111</v>
@@ -15858,7 +15858,7 @@
         <v>44760.24722222222</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44759.56388888889</v>
+        <v>44759.59166666667</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>44759.91944444444</v>
@@ -16042,7 +16042,7 @@
         <v>45191.94513888889</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45191.76041666666</v>
+        <v>45191.77013888889</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>45191.87291666667</v>
@@ -16135,7 +16135,7 @@
         <v>45487.50833333333</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45486.93611111111</v>
+        <v>45486.94236111111</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>45487.09930555556</v>
@@ -16857,7 +16857,7 @@
         <v>43752.34305555555</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>43751.79375</v>
+        <v>43751.80972222222</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>43752.02777777778</v>
@@ -16954,7 +16954,7 @@
         <v>43800.93194444444</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>43800.51597222222</v>
+        <v>43800.52361111111</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>43800.65972222222</v>
@@ -17328,7 +17328,7 @@
         <v>44165.68888888889</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44164.96319444444</v>
+        <v>44164.97986111111</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>44165.24027777778</v>
@@ -17421,7 +17421,7 @@
         <v>44166.35694444444</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44166.09861111111</v>
+        <v>44166.10277777778</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>44166.17847222222</v>
@@ -17787,7 +17787,7 @@
         <v>44345.46111111111</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44344.10833333333</v>
+        <v>44344.13194444445</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>44344.56388888889</v>
@@ -17884,7 +17884,7 @@
         <v>44559.76666666667</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44558.87430555555</v>
+        <v>44558.88611111111</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>44559.14444444444</v>
@@ -17981,7 +17981,7 @@
         <v>44609.29722222222</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44608.30972222222</v>
+        <v>44608.34305555555</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>44608.77152777778</v>
@@ -18074,7 +18074,7 @@
         <v>44696.60902777778</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44695.62847222222</v>
+        <v>44695.64375</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>44695.94236111111</v>
@@ -18262,7 +18262,7 @@
         <v>44792.00763888889</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44791.56111111111</v>
+        <v>44791.57222222222</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>44791.73472222222</v>
@@ -18355,7 +18355,7 @@
         <v>44802.3625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>44802.1125</v>
+        <v>44802.11597222222</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>44802.19027777778</v>
@@ -18448,7 +18448,7 @@
         <v>44810.03958333333</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44809.72708333333</v>
+        <v>44809.73333333333</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>44809.83541666667</v>
@@ -18727,7 +18727,7 @@
         <v>44938.30972222222</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>44937.98333333333</v>
+        <v>44937.99236111111</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>44938.11736111111</v>
@@ -18820,7 +18820,7 @@
         <v>44998.59166666667</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>44998.30069444444</v>
+        <v>44998.30347222222</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>44998.37847222222</v>
@@ -18913,7 +18913,7 @@
         <v>45119.28125</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45118.83819444444</v>
+        <v>45118.86666666667</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>45119.14930555555</v>
@@ -19006,7 +19006,7 @@
         <v>45123.27430555555</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45123.10625</v>
+        <v>45123.11319444444</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>45123.19097222222</v>
@@ -19099,7 +19099,7 @@
         <v>45126.51111111111</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45126.20763888889</v>
+        <v>45126.22013888889</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>45126.36458333334</v>
@@ -19192,7 +19192,7 @@
         <v>45126.87222222222</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45126.69722222222</v>
+        <v>45126.70277777778</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>45126.77638888889</v>
@@ -19380,7 +19380,7 @@
         <v>45144.72361111111</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45144.03263888889</v>
+        <v>45144.04722222222</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>45144.28402777778</v>
@@ -19473,7 +19473,7 @@
         <v>45145.15763888889</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45144.72430555556</v>
+        <v>45144.74305555555</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>45144.95763888889</v>
@@ -19566,7 +19566,7 @@
         <v>45145.96388888889</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45145.375</v>
+        <v>45145.39513888889</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>45145.65208333333</v>
@@ -19750,7 +19750,7 @@
         <v>45170.94861111111</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45170.38194444445</v>
+        <v>45170.41875</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>45170.78958333333</v>
@@ -19843,7 +19843,7 @@
         <v>45186.57708333333</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45186.10902777778</v>
+        <v>45186.11944444444</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>45186.28263888889</v>
@@ -20027,7 +20027,7 @@
         <v>45424.84097222222</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45424.58819444444</v>
+        <v>45424.59305555555</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>45424.67708333334</v>
@@ -20211,7 +20211,7 @@
         <v>45428.675</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45428.34513888889</v>
+        <v>45428.35416666666</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>45428.48055555556</v>
@@ -20395,7 +20395,7 @@
         <v>45430.01666666667</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45429.8375</v>
+        <v>45429.84583333333</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>45429.93819444445</v>
@@ -20583,7 +20583,7 @@
         <v>45592.72638888889</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45592.03402777778</v>
+        <v>45592.04652777778</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>45592.26736111111</v>
@@ -20676,7 +20676,7 @@
         <v>45608.14791666667</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45607.45138888889</v>
+        <v>45607.45694444444</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>45607.63472222222</v>
@@ -20970,7 +20970,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43539.375</v>
+        <v>43539.38888888889</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>43539.55416666667</v>
@@ -20998,11 +20998,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>30700</v>
+        <v>25810</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -21264,7 +21264,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>43751.79375</v>
+        <v>43751.80972222222</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>43752.02777777778</v>
@@ -21326,7 +21326,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>43800.51597222222</v>
+        <v>43800.52361111111</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>43800.65972222222</v>
@@ -21624,7 +21624,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>44005.1375</v>
+        <v>44005.15347222222</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>44005.37777777778</v>
@@ -21652,7 +21652,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>56443</v>
+        <v>48944</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>44007.48541666667</v>
+        <v>44007.50347222222</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>44007.80138888889</v>
@@ -21710,7 +21710,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>101023</v>
+        <v>89672</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>44086.43263888889</v>
+        <v>44086.44583333333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>44086.61458333334</v>
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>33411</v>
+        <v>28680</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>44164.96319444444</v>
+        <v>44164.97986111111</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>44165.24027777778</v>
@@ -21972,7 +21972,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>44166.09861111111</v>
+        <v>44166.10277777778</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>44166.17847222222</v>
@@ -22204,7 +22204,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>44344.10833333333</v>
+        <v>44344.13194444445</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>44344.56388888889</v>
@@ -22266,7 +22266,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>44346.33888888889</v>
+        <v>44346.36458333334</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>44346.68263888889</v>
@@ -22294,7 +22294,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>18544</v>
+        <v>16465</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>44357.19236111111</v>
+        <v>44357.24375</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>44357.83611111111</v>
@@ -22338,10 +22338,10 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>120</v>
@@ -22352,7 +22352,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>337992</v>
+        <v>279475</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>44359.25069444445</v>
+        <v>44359.26458333333</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>44359.52083333334</v>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>28210</v>
+        <v>23580</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>44371.06111111111</v>
+        <v>44371.08958333333</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>44371.52291666667</v>
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>218361</v>
+        <v>192245</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>44377.62361111111</v>
+        <v>44377.65416666667</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>44378.08263888889</v>
@@ -22556,7 +22556,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>44388.37916666667</v>
+        <v>44388.38472222222</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>44388.50138888889</v>
@@ -22672,7 +22672,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>44465.37152777778</v>
+        <v>44465.43055555555</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>44466.07361111111</v>
@@ -22700,7 +22700,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>255255</v>
+        <v>224115</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>44509.68194444444</v>
+        <v>44509.69166666667</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>44509.86041666667</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>32131</v>
+        <v>28680</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>44558.87430555555</v>
+        <v>44558.88611111111</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>44559.14444444444</v>
@@ -22850,7 +22850,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>44589.99722222222</v>
+        <v>44590.04375</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>44590.58263888889</v>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>352380</v>
+        <v>298378</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>44608.30972222222</v>
+        <v>44608.34305555555</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>44608.77152777778</v>
@@ -23024,7 +23024,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>44669.8625</v>
+        <v>44669.88402777778</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>44670.14652777778</v>
@@ -23052,7 +23052,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1596</v>
+        <v>325</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>44683.72083333333</v>
+        <v>44683.74166666667</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>44683.97916666666</v>
@@ -23110,7 +23110,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>67896</v>
+        <v>57291</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>44694.54513888889</v>
+        <v>44694.5625</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>44694.74861111111</v>
@@ -23198,7 +23198,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>44695.62847222222</v>
+        <v>44695.64375</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>44695.94236111111</v>
@@ -23256,7 +23256,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>44701.17986111111</v>
+        <v>44701.19583333333</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>44701.38194444445</v>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>41328</v>
+        <v>34980</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>44744.19583333333</v>
+        <v>44744.25972222222</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>44745.23194444444</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1107816</v>
+        <v>975106</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>44759.56388888889</v>
+        <v>44759.59166666667</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>44759.91944444444</v>
@@ -23608,7 +23608,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>44791.56111111111</v>
+        <v>44791.57222222222</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>44791.73472222222</v>
@@ -23724,7 +23724,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>44802.1125</v>
+        <v>44802.11597222222</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>44802.19027777778</v>
@@ -23782,7 +23782,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>44803.28263888889</v>
+        <v>44803.28680555556</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>44803.40763888889</v>
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7875</v>
+        <v>7140</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>44809.72708333333</v>
+        <v>44809.73333333333</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>44809.83541666667</v>
@@ -24192,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>44937.98333333333</v>
+        <v>44937.99236111111</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>44938.11736111111</v>
@@ -24250,7 +24250,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>44976.67152777778</v>
+        <v>44976.7</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>44977.01388888889</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>119805</v>
+        <v>100576</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>44995.20694444444</v>
+        <v>44995.21597222222</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>44995.30902777778</v>
@@ -24394,7 +24394,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10296</v>
+        <v>8515</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>44998.30069444444</v>
+        <v>44998.30347222222</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>44998.37847222222</v>
@@ -24482,7 +24482,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45039.25763888889</v>
+        <v>45039.27083333334</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>45039.40972222222</v>
@@ -24540,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45046.73194444444</v>
+        <v>45046.75555555556</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>45047.25972222222</v>
@@ -24598,7 +24598,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45057.6375</v>
+        <v>45057.66944444444</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>45058.07013888889</v>
@@ -24626,7 +24626,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>70987</v>
+        <v>68515</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45061.13125</v>
+        <v>45061.18055555555</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>45061.79652777778</v>
@@ -24670,21 +24670,21 @@
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>120</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>最近候选簇内有 3 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>455535</v>
+        <v>390286</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45064.28472222222</v>
+        <v>45064.325</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>45064.78263888889</v>
@@ -24888,7 +24888,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45118.83819444444</v>
+        <v>45118.86666666667</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>45119.14930555555</v>
@@ -24946,7 +24946,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45123.10625</v>
+        <v>45123.11319444444</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>45123.19097222222</v>
@@ -25004,7 +25004,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45126.20763888889</v>
+        <v>45126.22013888889</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>45126.36458333334</v>
@@ -25062,7 +25062,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45126.69722222222</v>
+        <v>45126.70277777778</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>45126.77638888889</v>
@@ -25182,7 +25182,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45144.03263888889</v>
+        <v>45144.04722222222</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>45144.28402777778</v>
@@ -25240,7 +25240,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45144.72430555556</v>
+        <v>45144.74305555555</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>45144.95763888889</v>
@@ -25298,7 +25298,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45145.375</v>
+        <v>45145.39513888889</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>45145.65208333333</v>
@@ -25472,7 +25472,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45170.38194444445</v>
+        <v>45170.41875</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>45170.78958333333</v>
@@ -25530,7 +25530,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45179.42013888889</v>
+        <v>45179.42847222222</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>45179.56666666667</v>
@@ -25558,7 +25558,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>21528</v>
+        <v>19110</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45186.10902777778</v>
+        <v>45186.11944444444</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>45186.28263888889</v>
@@ -25704,7 +25704,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45191.76041666666</v>
+        <v>45191.77013888889</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>45191.87291666667</v>
@@ -25732,7 +25732,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>12526</v>
+        <v>10405</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45227.43819444445</v>
+        <v>45227.45972222222</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>45227.87638888889</v>
@@ -25834,25 +25834,25 @@
         <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>120</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>196843</v>
+        <v>177871</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -25878,7 +25878,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45232.45208333333</v>
+        <v>45232.53541666667</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>45233.45486111111</v>
@@ -25902,11 +25902,11 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。最近候选簇内有 17 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>检测到 3 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。最近候选簇内有 17 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>924873</v>
+        <v>781158</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>1</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45234.39583333334</v>
+        <v>45234.42569444444</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>45234.77847222222</v>
@@ -25964,7 +25964,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>49141</v>
+        <v>36585</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45250.45972222222</v>
+        <v>45250.48888888889</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>45250.81597222222</v>
@@ -26052,7 +26052,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45253.16111111111</v>
+        <v>45253.18680555555</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>45253.52013888889</v>
@@ -26080,7 +26080,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>131806</v>
+        <v>113491</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45301.42569444444</v>
+        <v>45301.43402777778</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>45301.52708333333</v>
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>10153</v>
+        <v>8515</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45314.04305555556</v>
+        <v>45314.04652777778</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>45314.25277777778</v>
@@ -26428,7 +26428,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>44551</v>
+        <v>43071</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45330.18472222222</v>
+        <v>45330.19652777778</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>45330.35763888889</v>
@@ -26486,7 +26486,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>30135</v>
+        <v>26106</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45330.71180555555</v>
+        <v>45330.71388888889</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>45330.74166666667</v>
@@ -26544,7 +26544,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>615</v>
+        <v>501</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45338.18194444444</v>
+        <v>45338.23680555556</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>45338.85138888889</v>
@@ -26646,10 +26646,10 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>120</v>
@@ -26660,7 +26660,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>60615</v>
+        <v>36520</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45357.54166666666</v>
+        <v>45357.59236111111</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>45358.15</v>
@@ -26718,7 +26718,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>256179</v>
+        <v>254801</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45363.46597222222</v>
+        <v>45363.48333333333</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>45363.72638888889</v>
@@ -26776,7 +26776,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>69006</v>
+        <v>60031</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45365.90486111111</v>
+        <v>45365.93055555555</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>45366.25625</v>
@@ -26834,7 +26834,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>126253</v>
+        <v>108345</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45375.56111111111</v>
+        <v>45375.57083333333</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>45375.72083333333</v>
@@ -27066,7 +27066,7 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>25241</v>
+        <v>22168</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45390.38541666666</v>
+        <v>45390.40347222222</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>45390.57986111111</v>
@@ -27124,7 +27124,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>38226</v>
+        <v>31375</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45424.58819444444</v>
+        <v>45424.59305555555</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>45424.67708333334</v>
@@ -27444,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45426.77847222222</v>
+        <v>45426.78680555556</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>45426.88263888889</v>
@@ -27472,7 +27472,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1596</v>
+        <v>990</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45428.34513888889</v>
+        <v>45428.35416666666</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>45428.48055555556</v>
@@ -27618,7 +27618,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45429.8375</v>
+        <v>45429.84583333333</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>45429.93819444445</v>
@@ -27680,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45480.56875</v>
+        <v>45480.57986111111</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>45480.78263888889</v>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>46360</v>
+        <v>41616</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45486.93611111111</v>
+        <v>45486.94236111111</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>45487.09930555556</v>
@@ -27766,7 +27766,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>26796</v>
+        <v>24753</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45502.04236111111</v>
+        <v>45502.06111111111</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>45502.29652777778</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>65703</v>
+        <v>56280</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>1</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45513.49375</v>
+        <v>45513.50694444445</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>45513.71388888889</v>
@@ -28042,21 +28042,21 @@
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
         <v>120</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>49141</v>
+        <v>43365</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45517.62291666667</v>
+        <v>45517.66180555556</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>45518.17222222222</v>
@@ -28390,21 +28390,21 @@
         <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
         <v>120</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>169618</v>
+        <v>138566</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>1</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45530.10694444444</v>
+        <v>45530.14930555555</v>
       </c>
       <c r="G132" s="2" t="n">
         <v>45530.75069444445</v>
@@ -28462,11 +28462,11 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>224785</v>
+        <v>185745</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
@@ -28492,7 +28492,7 @@
         <v>1</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45536.72708333333</v>
+        <v>45536.75694444445</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>45537.0875</v>
@@ -28550,7 +28550,7 @@
         <v>1</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45544.85416666666</v>
+        <v>45544.86597222222</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>45544.99027777778</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>18528</v>
+        <v>15400</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>1</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45545.58611111111</v>
+        <v>45545.59444444445</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>45545.69652777778</v>
@@ -28636,7 +28636,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>12090</v>
+        <v>10296</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>1</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45546.07361111111</v>
+        <v>45546.08333333334</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>45546.19652777778</v>
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>15051</v>
+        <v>12720</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>1</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45550.60555555556</v>
+        <v>45550.61458333334</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>45550.71597222222</v>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>11001</v>
+        <v>9570</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>1</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45569.01180555556</v>
+        <v>45569.02638888889</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>45569.17569444444</v>
@@ -28796,21 +28796,21 @@
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L138" t="n">
         <v>120</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 4 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>12595</v>
+        <v>9294</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>1</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45592.03402777778</v>
+        <v>45592.04652777778</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>45592.26736111111</v>
@@ -28898,7 +28898,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45607.45138888889</v>
+        <v>45607.45694444444</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>45607.63472222222</v>
@@ -28956,7 +28956,7 @@
         <v>1</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45648.25625</v>
+        <v>45648.26319444444</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>45648.34722222222</v>
@@ -28984,7 +28984,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>8128</v>
+        <v>6903</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45679.82083333333</v>
+        <v>45679.83125</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>45679.96111111111</v>
@@ -29042,7 +29042,7 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>19701</v>
+        <v>16836</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45680.13611111111</v>
+        <v>45680.14166666667</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>45680.29791666667</v>
@@ -29100,7 +29100,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>26335</v>
+        <v>24531</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45692.34375</v>
+        <v>45692.41041666667</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>45693.22083333333</v>
@@ -29246,7 +29246,7 @@
         <v>1</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45773.07152777778</v>
+        <v>45773.07916666667</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>45773.19583333333</v>
@@ -29274,7 +29274,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>15400</v>
+        <v>13530</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
